--- a/education_forms/035_language_acquisition_plan_form_template--education_forms.xlsx
+++ b/education_forms/035_language_acquisition_plan_form_template--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -918,8 +918,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -947,12 +947,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'beginner',_'label':_'beginner'}</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'beginner', 'label': 'Beginner'}</t>
+          <t>Beginner</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'intermediate',_'label':_'intermediate'}</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'intermediate', 'label': 'Intermediate'}</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'advanced',_'label':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'advanced', 'label': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'reading',_'label':_'reading'}</t>
+          <t>reading</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'reading', 'label': 'Reading'}</t>
+          <t>Reading</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'writing',_'label':_'writing'}</t>
+          <t>writing</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'writing', 'label': 'Writing'}</t>
+          <t>Writing</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'speaking',_'label':_'speaking'}</t>
+          <t>speaking</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'speaking', 'label': 'Speaking'}</t>
+          <t>Speaking</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'listening',_'label':_'listening'}</t>
+          <t>listening</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'listening', 'label': 'Listening'}</t>
+          <t>Listening</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'novice',_'label':_'novice'}</t>
+          <t>novice</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'novice', 'label': 'Novice'}</t>
+          <t>Novice</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'intermediate',_'label':_'intermediate'}</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'intermediate', 'label': 'Intermediate'}</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'advanced',_'label':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'advanced', 'label': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'daily',_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'daily', 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'weekly',_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'weekly', 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'monthly',_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'monthly', 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
